--- a/Excel/Proto/Test.xlsx
+++ b/Excel/Proto/Test.xlsx
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,6 +417,9 @@
       <c r="B1" t="str">
         <v>Name</v>
       </c>
+      <c r="C1" t="str">
+        <v>#주석열</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -425,6 +428,9 @@
       <c r="B2" t="str">
         <v>str</v>
       </c>
+      <c r="C2" t="str">
+        <v>ㄹㅁ</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -433,13 +439,29 @@
       <c r="B3" t="str">
         <v>1</v>
       </c>
+      <c r="C3" t="str">
+        <v>ㅎㅁ</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="str">
+        <v>ㄴㅁㅎ</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1</v>
+        <v>#주석행</v>
       </c>
       <c r="B5" t="str">
         <v>1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ㄴㅁㅇㅎ</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="str">
+        <v>ㄴㅁㅇ</v>
       </c>
     </row>
     <row r="7">
@@ -449,10 +471,13 @@
       <c r="B7" t="str">
         <v>3</v>
       </c>
+      <c r="C7" t="str">
+        <v>ㅎ</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>